--- a/artfynd/A 33224-2024 artfynd.xlsx
+++ b/artfynd/A 33224-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119659447</v>
+        <v>119659461</v>
       </c>
       <c r="B2" t="n">
-        <v>100171</v>
+        <v>101249</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -769,7 +769,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Skogsbryn</t>
+          <t>Vägren</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119659461</v>
+        <v>119659447</v>
       </c>
       <c r="B3" t="n">
-        <v>101249</v>
+        <v>100171</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221317</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Vägren</t>
+          <t>Skogsbryn</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
